--- a/tables/ae_per_row_anomaly_count_metrics.xlsx
+++ b/tables/ae_per_row_anomaly_count_metrics.xlsx
@@ -453,22 +453,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="C2" t="n">
-        <v>209</v>
+        <v>242</v>
       </c>
       <c r="D2" t="n">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>0.461</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>0.539</t>
         </is>
       </c>
     </row>
@@ -477,22 +477,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="C3" t="n">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="D3" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>0.584</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>0.416</t>
         </is>
       </c>
     </row>
@@ -501,22 +501,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="C4" t="n">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="D4" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>0.816</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>0.184</t>
         </is>
       </c>
     </row>

--- a/tables/ae_per_row_anomaly_count_metrics.xlsx
+++ b/tables/ae_per_row_anomaly_count_metrics.xlsx
@@ -453,22 +453,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="C2" t="n">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="D2" t="n">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>0.406</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>0.594</t>
         </is>
       </c>
     </row>
@@ -477,22 +477,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="C3" t="n">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="D3" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>0.607</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.393</t>
         </is>
       </c>
     </row>
@@ -501,22 +501,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="C4" t="n">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="D4" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>0.784</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.216</t>
         </is>
       </c>
     </row>

--- a/tables/ae_per_row_anomaly_count_metrics.xlsx
+++ b/tables/ae_per_row_anomaly_count_metrics.xlsx
@@ -456,19 +456,19 @@
         <v>515</v>
       </c>
       <c r="C2" t="n">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="D2" t="n">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>0.435</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>0.565</t>
         </is>
       </c>
     </row>
@@ -480,19 +480,19 @@
         <v>399</v>
       </c>
       <c r="C3" t="n">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D3" t="n">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>0.637</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>0.363</t>
         </is>
       </c>
     </row>
@@ -504,19 +504,19 @@
         <v>333</v>
       </c>
       <c r="C4" t="n">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="D4" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>0.817</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>0.183</t>
         </is>
       </c>
     </row>

--- a/tables/ae_per_row_anomaly_count_metrics.xlsx
+++ b/tables/ae_per_row_anomaly_count_metrics.xlsx
@@ -419,12 +419,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># Anomalies in Row</t>
+          <t>Anzahl Anomalien pro Zeile</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t>Anzahl</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -444,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Miss Rate</t>
+          <t>Miss-Rate</t>
         </is>
       </c>
     </row>
